--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\NSE1 IMPORTANT DATES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\NSE-1-Important-Dates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="140">
   <si>
     <t>Country</t>
   </si>
@@ -1346,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="5">
-        <v>46368</v>
+        <v>46371</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>139</v>
@@ -1359,8 +1359,8 @@
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>43</v>
+      <c r="B37" s="5">
+        <v>46073</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>85</v>
@@ -1618,7 +1618,7 @@
         <v>101</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -440,6 +440,12 @@
   </si>
   <si>
     <t>Jamhuri Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya </t>
+  </si>
+  <si>
+    <t>JSB Bday</t>
   </si>
 </sst>
 </file>
@@ -842,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -1343,13 +1349,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46371</v>
+        <v>46230</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>132</v>
@@ -1357,30 +1363,30 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B37" s="5">
-        <v>46073</v>
+        <v>46371</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>28</v>
+      <c r="B38" s="5">
+        <v>46073</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1388,10 +1394,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>132</v>
@@ -1402,10 +1408,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>132</v>
@@ -1416,10 +1422,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>132</v>
@@ -1427,16 +1433,16 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1444,10 +1450,10 @@
         <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>130</v>
@@ -1458,13 +1464,13 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1472,10 +1478,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>132</v>
@@ -1483,13 +1489,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>132</v>
@@ -1500,10 +1506,10 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>132</v>
@@ -1514,10 +1520,10 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>132</v>
@@ -1528,10 +1534,10 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>132</v>
@@ -1539,16 +1545,16 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1556,27 +1562,27 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1584,10 +1590,10 @@
         <v>10</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>130</v>
@@ -1598,10 +1604,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>130</v>
@@ -1612,13 +1618,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1626,13 +1632,13 @@
         <v>10</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1640,10 +1646,10 @@
         <v>10</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -1657,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>132</v>
@@ -1668,10 +1674,10 @@
         <v>10</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>132</v>
@@ -1682,10 +1688,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>132</v>
@@ -1693,16 +1699,16 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -1710,22 +1716,24 @@
         <v>11</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -1734,10 +1742,10 @@
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1746,10 +1754,10 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1758,10 +1766,10 @@
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -1773,21 +1781,19 @@
         <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>132</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>132</v>
@@ -1798,10 +1804,10 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>132</v>
@@ -1812,10 +1818,10 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>132</v>
@@ -1826,10 +1832,10 @@
         <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>132</v>
@@ -1840,10 +1846,10 @@
         <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>132</v>
@@ -1854,10 +1860,10 @@
         <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>132</v>
@@ -1865,13 +1871,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>132</v>
@@ -1879,13 +1885,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>132</v>
@@ -1896,10 +1902,10 @@
         <v>13</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>132</v>
@@ -1907,13 +1913,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>132</v>
@@ -1924,10 +1930,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>132</v>
@@ -1941,7 +1947,7 @@
         <v>20</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>132</v>
@@ -1952,10 +1958,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>132</v>
@@ -1966,10 +1972,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>132</v>
@@ -1980,12 +1986,26 @@
         <v>14</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2002,7 +2022,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="141">
   <si>
     <t>Country</t>
   </si>
@@ -442,10 +442,7 @@
     <t>Jamhuri Day</t>
   </si>
   <si>
-    <t xml:space="preserve">Kenya </t>
-  </si>
-  <si>
-    <t>JSB Bday</t>
+    <t>JSB BDAY</t>
   </si>
 </sst>
 </file>
@@ -521,7 +518,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF16AA06"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1349,13 +1367,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="B36" s="5">
         <v>46230</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>132</v>
@@ -2010,7 +2028,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
+  <conditionalFormatting sqref="D1:D35 D37:D1048576">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"Yet to Happen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Postponed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>"Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>JSB BDAY</t>
+  </si>
+  <si>
+    <t>JSB Dad BDAY</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF16AA06"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -866,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -2027,8 +2051,33 @@
         <v>132</v>
       </c>
     </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B84" s="5">
+        <v>46234</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D35 D37:D1048576">
+  <conditionalFormatting sqref="D1:D35 D37:D83 D85:D1048576">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+      <formula>"Yet to Happen"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Postponed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+      <formula>"Executed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D36">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2039,7 +2088,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D36">
+  <conditionalFormatting sqref="D84">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2051,7 +2100,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D84">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="144">
   <si>
     <t>Country</t>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>JSB Dad BDAY</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The event went rather well with over 200 people having to show what they are made of as mechanics. Winner gets an all expense paid trip to India </t>
   </si>
 </sst>
 </file>
@@ -477,7 +483,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -500,11 +506,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -517,6 +534,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,16 +911,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
     <col min="2" max="2" width="14.54296875" customWidth="1"/>
     <col min="3" max="3" width="66.453125" customWidth="1"/>
     <col min="4" max="4" width="16.6328125" customWidth="1"/>
+    <col min="5" max="5" width="32.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,8 +934,11 @@
       <c r="D1" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -926,8 +951,11 @@
       <c r="D2" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -941,7 +969,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -955,7 +983,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -969,7 +997,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -983,7 +1011,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -997,7 +1025,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1011,7 +1039,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1025,7 +1053,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1067,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1053,7 +1081,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1095,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
@@ -1081,7 +1109,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1123,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -1109,7 +1137,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -2066,7 +2094,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D35 D37:D83 D85:D1048576">
+  <conditionalFormatting sqref="D1:D35 D37:D83 D85:D1048576 E1:E2">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -440,12 +440,6 @@
   </si>
   <si>
     <t>Jamhuri Day</t>
-  </si>
-  <si>
-    <t>JSB BDAY</t>
-  </si>
-  <si>
-    <t>JSB Dad BDAY</t>
   </si>
   <si>
     <t>Description</t>
@@ -542,49 +536,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF16AA06"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF16AA06"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -911,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -935,7 +887,7 @@
         <v>129</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -952,7 +904,7 @@
         <v>130</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1422,10 +1374,10 @@
         <v>5</v>
       </c>
       <c r="B36" s="5">
-        <v>46230</v>
+        <v>46371</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>132</v>
@@ -1433,30 +1385,30 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B37" s="5">
-        <v>46371</v>
+        <v>46073</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="5">
-        <v>46073</v>
+      <c r="B38" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1464,10 +1416,10 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>132</v>
@@ -1478,10 +1430,10 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>132</v>
@@ -1492,10 +1444,10 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>132</v>
@@ -1503,16 +1455,16 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1520,10 +1472,10 @@
         <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>130</v>
@@ -1534,13 +1486,13 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1548,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>132</v>
@@ -1559,13 +1511,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>132</v>
@@ -1576,10 +1528,10 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>132</v>
@@ -1590,10 +1542,10 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>132</v>
@@ -1604,10 +1556,10 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>132</v>
@@ -1615,16 +1567,16 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1632,27 +1584,27 @@
         <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1660,10 +1612,10 @@
         <v>10</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>130</v>
@@ -1674,10 +1626,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>130</v>
@@ -1688,13 +1640,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1702,13 +1654,13 @@
         <v>10</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1716,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -1733,7 +1685,7 @@
         <v>20</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>132</v>
@@ -1744,10 +1696,10 @@
         <v>10</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>132</v>
@@ -1758,10 +1710,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>132</v>
@@ -1769,16 +1721,16 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -1786,24 +1738,22 @@
         <v>11</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -1812,10 +1762,10 @@
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1824,10 +1774,10 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1836,10 +1786,10 @@
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -1851,19 +1801,21 @@
         <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>132</v>
@@ -1874,10 +1826,10 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>132</v>
@@ -1888,10 +1840,10 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>132</v>
@@ -1902,10 +1854,10 @@
         <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>132</v>
@@ -1916,10 +1868,10 @@
         <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>132</v>
@@ -1930,10 +1882,10 @@
         <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>132</v>
@@ -1941,13 +1893,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>132</v>
@@ -1955,13 +1907,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>132</v>
@@ -1972,10 +1924,10 @@
         <v>13</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>132</v>
@@ -1983,13 +1935,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>132</v>
@@ -2000,10 +1952,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>132</v>
@@ -2017,7 +1969,7 @@
         <v>20</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>132</v>
@@ -2028,10 +1980,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>132</v>
@@ -2042,10 +1994,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>132</v>
@@ -2056,79 +2008,29 @@
         <v>14</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B84" s="5">
-        <v>46234</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D35 D37:D83 D85:D1048576 E1:E2">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+  <conditionalFormatting sqref="D1:D1048576 E1:E2">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"Executed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"Yet to Happen"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Postponed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
-      <formula>"Executed"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D84">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"Yet to Happen"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"Postponed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D84">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D82">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="143">
   <si>
     <t>Country</t>
   </si>
@@ -223,12 +223,6 @@
     <t>Ronin &amp; Ntorq Launch</t>
   </si>
   <si>
-    <t>Ramadan Advertisements in TV and Social Media</t>
-  </si>
-  <si>
-    <t>Local Football sponsor with HLX range promotions</t>
-  </si>
-  <si>
     <t>XL 100  Dealer launch</t>
   </si>
   <si>
@@ -292,9 +286,6 @@
     <t>AOG 80kms ride to Mazagan Beach</t>
   </si>
   <si>
-    <t>Anniversary Celebration / Mass Delivery</t>
-  </si>
-  <si>
     <t>Apache AOG rides &amp; stunt show at Sindibad</t>
   </si>
   <si>
@@ -313,9 +304,6 @@
     <t>Virtual Distributor Conference</t>
   </si>
   <si>
-    <t>Virtual Distributor Conference 2.0</t>
-  </si>
-  <si>
     <t>TVS South Africa Country Launch</t>
   </si>
   <si>
@@ -328,21 +316,9 @@
     <t>Store Inaugration  Centurion, Pretoria,</t>
   </si>
   <si>
-    <t>Tie ups with Riding School</t>
-  </si>
-  <si>
-    <t>Store Inaugration  Ekrold, Durban</t>
-  </si>
-  <si>
     <t>HLX Day-Cape Town</t>
   </si>
   <si>
-    <t>India Visit- 7 Dealers</t>
-  </si>
-  <si>
-    <t>Store Inaugration  Tex,George</t>
-  </si>
-  <si>
     <t>HLX Day – Dar es Salaam</t>
   </si>
   <si>
@@ -439,20 +415,47 @@
     <t xml:space="preserve">Tris academy launch </t>
   </si>
   <si>
-    <t>Jamhuri Day</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t xml:space="preserve">The event went rather well with over 200 people having to show what they are made of as mechanics. Winner gets an all expense paid trip to India </t>
+  </si>
+  <si>
+    <t>Q1 Townhall</t>
+  </si>
+  <si>
+    <t>Apache RTR 310 Launch</t>
+  </si>
+  <si>
+    <t>TVS Apache RTR 310 Morocco Launch marked TVS Motor Company’s entry into Africa’s premium motorcycle segment. The launch introduced the high-performance RTR 310 as a flagship “Track to Road” model for the growing 200–350cc market in Morocco.</t>
+  </si>
+  <si>
+    <t>The TVS King Deluxe Plus was introduced in Fort Dauphin, Madagascar, by late March 2026, highlighted as a strong and durable three-wheeler for the city's hilly terrain. This launch expands the presence of TVS Motor Company in Madagascar, featuring a reliable 3W designed for both passenger and commercial use throughout the island.</t>
+  </si>
+  <si>
+    <t>Bikers WareHouse Store Inauguration</t>
+  </si>
+  <si>
+    <t>I-Qube Launch</t>
+  </si>
+  <si>
+    <t>NTORQ150 &amp; RAIDER i-Go Launch</t>
+  </si>
+  <si>
+    <t>Riding School Collaboration with King Donut</t>
+  </si>
+  <si>
+    <t>Riding School Collaboration with Prestige Bikes</t>
+  </si>
+  <si>
+    <t>TVS Centurion 3S inaugartion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,6 +471,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -477,7 +487,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -511,11 +521,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -532,6 +557,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,14 +890,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
     <col min="2" max="2" width="14.54296875" customWidth="1"/>
     <col min="3" max="3" width="66.453125" customWidth="1"/>
     <col min="4" max="4" width="16.6328125" customWidth="1"/>
-    <col min="5" max="5" width="32.08984375" customWidth="1"/>
+    <col min="5" max="5" width="124.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -884,10 +911,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -901,10 +928,10 @@
         <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -918,7 +945,7 @@
         <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -932,7 +959,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -946,7 +973,7 @@
         <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -960,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -974,7 +1001,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -988,7 +1015,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1002,7 +1029,7 @@
         <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1016,7 +1043,7 @@
         <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1030,7 +1057,7 @@
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1044,7 +1071,7 @@
         <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1058,7 +1085,7 @@
         <v>66</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1066,13 +1093,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1080,13 +1107,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1094,41 +1121,41 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46079</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1136,27 +1163,27 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="3">
-        <v>46079</v>
+      <c r="B20" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1164,13 +1191,13 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1178,13 +1205,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1192,13 +1219,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1206,13 +1233,13 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1220,13 +1247,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1234,13 +1261,13 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1248,13 +1275,13 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1262,13 +1289,13 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1276,13 +1303,13 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1290,13 +1317,13 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1304,13 +1331,13 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1318,279 +1345,285 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46073</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="5">
-        <v>46371</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="5">
-        <v>46073</v>
+      <c r="B37" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46133</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1598,125 +1631,125 @@
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>99</v>
+      <c r="B53" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>100</v>
+      <c r="B54" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>101</v>
+      <c r="B55" s="5">
+        <v>46137</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>19</v>
+      <c r="B56" s="5">
+        <v>46151</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>20</v>
+      <c r="B57" s="5">
+        <v>46188</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>104</v>
+      <c r="B58" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>105</v>
+      <c r="B59" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -1724,24 +1757,22 @@
         <v>11</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -1750,10 +1781,10 @@
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -1762,10 +1793,10 @@
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1774,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1789,22 +1820,24 @@
         <v>51</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -1812,13 +1845,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -1826,13 +1859,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -1840,13 +1873,13 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -1854,13 +1887,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -1868,41 +1901,41 @@
         <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
@@ -1910,27 +1943,27 @@
         <v>13</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -1938,13 +1971,13 @@
         <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -1955,10 +1988,10 @@
         <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -1966,13 +1999,13 @@
         <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -1980,13 +2013,13 @@
         <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -1994,31 +2027,17 @@
         <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576 E1:E2">
+  <conditionalFormatting sqref="E1:E2 E35 D1:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2030,7 +2049,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D82">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D81">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -235,18 +235,12 @@
     <t>HLX Day-Kisii</t>
   </si>
   <si>
-    <t>Silver Groove and Saatwai dealer opening</t>
-  </si>
-  <si>
     <t>Nyeri Polytechnic PTC - Inaguration</t>
   </si>
   <si>
     <t>Motorsport excellence award</t>
   </si>
   <si>
-    <t>Boda Girls Launch</t>
-  </si>
-  <si>
     <t>AOG Flag off</t>
   </si>
   <si>
@@ -370,9 +364,6 @@
     <t>Pre launch Campaign</t>
   </si>
   <si>
-    <t>TVS Zambia Country Launch</t>
-  </si>
-  <si>
     <t>3S Inauguration – Lusaka</t>
   </si>
   <si>
@@ -449,6 +440,12 @@
   </si>
   <si>
     <t>TVS Centurion 3S inaugartion</t>
+  </si>
+  <si>
+    <t>First Distributor Conference Successful</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -890,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -911,10 +908,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -928,10 +925,10 @@
         <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -945,7 +942,7 @@
         <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -959,7 +956,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -973,7 +970,7 @@
         <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -987,7 +984,7 @@
         <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1001,7 +998,7 @@
         <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1015,7 +1012,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1029,7 +1026,7 @@
         <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1043,7 +1040,7 @@
         <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1057,7 +1054,7 @@
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1071,7 +1068,7 @@
         <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1085,7 +1082,7 @@
         <v>66</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1099,7 +1096,7 @@
         <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1113,7 +1110,7 @@
         <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1127,7 +1124,7 @@
         <v>69</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1138,10 +1135,10 @@
         <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1152,10 +1149,10 @@
         <v>46079</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1166,10 +1163,10 @@
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1180,10 +1177,10 @@
         <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1197,7 +1194,7 @@
         <v>70</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1205,13 +1202,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1219,13 +1216,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1233,13 +1230,13 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1247,13 +1244,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1261,13 +1258,13 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1275,13 +1272,13 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1289,13 +1286,13 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1303,13 +1300,13 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1317,13 +1314,13 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1331,55 +1328,58 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46073</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="5">
-        <v>46073</v>
+      <c r="B34" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1387,16 +1387,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1404,41 +1401,41 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1446,13 +1443,16 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1460,44 +1460,41 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1505,13 +1502,13 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1519,69 +1516,72 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46133</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="5">
-        <v>46133</v>
+        <v>10</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1589,13 +1589,13 @@
         <v>10</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1603,41 +1603,41 @@
         <v>10</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
+      <c r="B51" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>97</v>
+      <c r="B52" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1645,13 +1645,13 @@
         <v>10</v>
       </c>
       <c r="B53" s="5">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -1659,13 +1659,13 @@
         <v>10</v>
       </c>
       <c r="B54" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>141</v>
+        <v>46151</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -1673,13 +1673,13 @@
         <v>10</v>
       </c>
       <c r="B55" s="5">
-        <v>46137</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>142</v>
+        <v>46188</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1687,13 +1687,13 @@
         <v>10</v>
       </c>
       <c r="B56" s="5">
-        <v>46151</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>46191</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>135</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1701,63 +1701,59 @@
         <v>10</v>
       </c>
       <c r="B57" s="5">
-        <v>46188</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>137</v>
+        <v>46193</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="5">
-        <v>46191</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>138</v>
+        <v>11</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="5">
-        <v>46193</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>124</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>100</v>
@@ -1769,7 +1765,7 @@
         <v>11</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>101</v>
@@ -1781,7 +1777,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>102</v>
@@ -1793,37 +1789,41 @@
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -1831,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -1845,13 +1845,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -1859,13 +1859,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -1873,83 +1873,83 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>111</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -1957,13 +1957,13 @@
         <v>14</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -1971,13 +1971,13 @@
         <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -1985,13 +1985,13 @@
         <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -1999,45 +1999,17 @@
         <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E2 E35 D1:D1048576">
+  <conditionalFormatting sqref="E1:E2 E33 D1:D1048576 E45">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2049,7 +2021,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D81">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D79">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -1734,7 +1734,9 @@
       <c r="C59" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D59" s="2"/>
+      <c r="D59" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
@@ -1746,7 +1748,9 @@
       <c r="C60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
@@ -1758,7 +1762,9 @@
       <c r="C61" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
@@ -1770,7 +1776,9 @@
       <c r="C62" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
@@ -1782,7 +1790,9 @@
       <c r="C63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="2"/>
+      <c r="D63" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
@@ -1798,7 +1808,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -1809,10 +1819,10 @@
         <v>104</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -1823,10 +1833,10 @@
         <v>105</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
@@ -1837,10 +1847,10 @@
         <v>106</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -1854,7 +1864,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -1868,7 +1878,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
@@ -1882,7 +1892,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -1896,7 +1906,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>13</v>
       </c>
@@ -1910,7 +1920,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -1924,7 +1934,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>14</v>
       </c>
@@ -1935,10 +1945,13 @@
         <v>113</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>14</v>
       </c>
@@ -1946,70 +1959,56 @@
         <v>20</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E2 E33 D1:D1048576 E45">
+  <conditionalFormatting sqref="E1:E2 E33 E45 D1:D1048576 E74">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2021,7 +2020,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D78">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="142">
   <si>
     <t>Country</t>
   </si>
@@ -445,7 +445,7 @@
     <t>First Distributor Conference Successful</t>
   </si>
   <si>
-    <t>s</t>
+    <t>Zambia Product line Launch</t>
   </si>
 </sst>
 </file>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -1947,9 +1947,7 @@
       <c r="D74" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>141</v>
-      </c>
+      <c r="E74" s="7"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
@@ -1969,11 +1967,11 @@
       <c r="A76" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>54</v>
+      <c r="B76" s="5">
+        <v>46132</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>121</v>
@@ -1984,10 +1982,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>121</v>
@@ -1998,12 +1996,26 @@
         <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2020,7 +2032,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D78">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D79">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -13,14 +13,13 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="145">
   <si>
     <t>Country</t>
   </si>
@@ -139,15 +138,6 @@
     <t>28-Mar-2026</t>
   </si>
   <si>
-    <t>22-Apr-2026</t>
-  </si>
-  <si>
-    <t>07-May-2026</t>
-  </si>
-  <si>
-    <t>23-May-2026</t>
-  </si>
-  <si>
     <t>28-May-2026</t>
   </si>
   <si>
@@ -226,9 +216,6 @@
     <t>XL 100  Dealer launch</t>
   </si>
   <si>
-    <t>Raider 125 launch</t>
-  </si>
-  <si>
     <t>ARE &amp; APP</t>
   </si>
   <si>
@@ -241,18 +228,12 @@
     <t>Motorsport excellence award</t>
   </si>
   <si>
-    <t>AOG Flag off</t>
-  </si>
-  <si>
     <t>HLX family day - Eldoret</t>
   </si>
   <si>
     <t>TVS iQube Launch</t>
   </si>
   <si>
-    <t>RR 310 Launch</t>
-  </si>
-  <si>
     <t>Meru C&amp;G branch inauguration</t>
   </si>
   <si>
@@ -446,6 +427,33 @@
   </si>
   <si>
     <t>Zambia Product line Launch</t>
+  </si>
+  <si>
+    <t>HLX DAY</t>
+  </si>
+  <si>
+    <t>Livingstone Riders Event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zambia </t>
+  </si>
+  <si>
+    <t>Service Camp</t>
+  </si>
+  <si>
+    <t>RR 310 Showroom Launch</t>
+  </si>
+  <si>
+    <t>AOG Ride</t>
+  </si>
+  <si>
+    <t>ARE Event</t>
+  </si>
+  <si>
+    <t>Raider 125 launch &amp; Dealer Meet</t>
+  </si>
+  <si>
+    <t>RR 310 Launch &amp; AOG Flag off</t>
   </si>
 </sst>
 </file>
@@ -887,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -908,10 +916,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -922,13 +930,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -939,10 +947,10 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -953,10 +961,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -967,10 +975,10 @@
         <v>46122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -981,10 +989,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -995,10 +1003,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1009,10 +1017,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1023,24 +1031,24 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>23</v>
+      <c r="B10" s="5">
+        <v>46185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1048,13 +1056,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1062,27 +1070,27 @@
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1090,69 +1098,69 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
+      <c r="B15" s="5">
+        <v>46158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>30</v>
+      <c r="B16" s="5">
+        <v>46167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46203</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46079</v>
+        <v>4</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46259</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1160,27 +1168,27 @@
         <v>5</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>34</v>
+      <c r="B20" s="3">
+        <v>46079</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1188,13 +1196,13 @@
         <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1202,13 +1210,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1216,13 +1224,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1230,13 +1238,13 @@
         <v>5</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1244,13 +1252,13 @@
         <v>5</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1258,41 +1266,41 @@
         <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
+      <c r="B27" s="5">
+        <v>46188</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>42</v>
+      <c r="B28" s="5">
+        <v>46179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1300,13 +1308,13 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1314,58 +1322,55 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>25</v>
+      <c r="B31" s="5">
+        <v>46399</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="5">
-        <v>46073</v>
+        <v>5</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>28</v>
+      <c r="B33" s="5">
+        <v>46073</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1373,13 +1378,16 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1387,13 +1395,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1401,27 +1409,27 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1429,13 +1437,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1443,16 +1451,13 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1460,352 +1465,347 @@
         <v>7</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46151</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="B43" s="5">
+        <v>46165</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>30</v>
+        <v>7</v>
+      </c>
+      <c r="B44" s="5">
+        <v>46249</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>140</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" s="5">
-        <v>46133</v>
+        <v>8</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B51" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>137</v>
+        <v>46133</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>138</v>
+      <c r="B52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B53" s="5">
-        <v>46137</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>139</v>
+      <c r="B53" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="5">
-        <v>46151</v>
+      <c r="B54" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="5">
-        <v>46188</v>
+      <c r="B55" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B56" s="5">
-        <v>46191</v>
+        <v>46136</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="5">
+        <v>46137</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="5">
+        <v>46151</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46188</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B61" s="5">
+        <v>46191</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="5">
         <v>46193</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>101</v>
+      <c r="C62" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -1813,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -1827,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -1841,13 +1841,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -1855,13 +1855,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -1869,13 +1869,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -1883,126 +1883,125 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E74" s="7"/>
+        <v>115</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="5">
-        <v>46132</v>
+        <v>12</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -2010,17 +2009,116 @@
         <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="5">
+        <v>46132</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="5">
+        <v>46164</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B85" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>121</v>
+      <c r="C86" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E2 E33 E45 D1:D1048576 E74">
+  <conditionalFormatting sqref="E1:E2 E34 E50 E79 D1:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2032,20 +2130,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D86">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$84</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="143">
   <si>
     <t>Country</t>
   </si>
@@ -138,9 +141,6 @@
     <t>28-Mar-2026</t>
   </si>
   <si>
-    <t>28-May-2026</t>
-  </si>
-  <si>
     <t>20-Feb-2026</t>
   </si>
   <si>
@@ -262,9 +262,6 @@
   </si>
   <si>
     <t>Apache AOG rides &amp; stunt show at Sindibad</t>
-  </si>
-  <si>
-    <t>Influencer Campaign – Maputo</t>
   </si>
   <si>
     <t>3S &amp; PTC Inauguration – Beira</t>
@@ -895,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -916,10 +913,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -930,13 +927,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -947,10 +944,10 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -961,10 +958,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -975,10 +972,10 @@
         <v>46122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -989,10 +986,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1003,10 +1000,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1017,10 +1014,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1031,10 +1028,10 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1045,10 +1042,10 @@
         <v>46185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1059,10 +1056,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1073,10 +1070,10 @@
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1087,10 +1084,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1101,10 +1098,10 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1115,10 +1112,10 @@
         <v>46158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1129,10 +1126,10 @@
         <v>46167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1143,10 +1140,10 @@
         <v>46203</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1157,10 +1154,10 @@
         <v>46259</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1171,10 +1168,10 @@
         <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1185,10 +1182,10 @@
         <v>46079</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1199,10 +1196,10 @@
         <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1213,10 +1210,10 @@
         <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1227,24 +1224,24 @@
         <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>37</v>
+      <c r="B24" s="5">
+        <v>46213</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1255,10 +1252,10 @@
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1269,10 +1266,10 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1283,10 +1280,10 @@
         <v>46188</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1297,38 +1294,38 @@
         <v>46179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>39</v>
+      <c r="B29" s="5">
+        <v>46201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>23</v>
+      <c r="B30" s="5">
+        <v>46205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1339,24 +1336,24 @@
         <v>46399</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>25</v>
+      <c r="B32" s="5">
+        <v>46198</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1367,10 +1364,10 @@
         <v>46073</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1381,13 +1378,13 @@
         <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1395,13 +1392,13 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1412,10 +1409,10 @@
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1426,10 +1423,10 @@
         <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1440,10 +1437,10 @@
         <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1451,13 +1448,13 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1468,13 +1465,13 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1482,13 +1479,13 @@
         <v>7</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -1499,10 +1496,10 @@
         <v>46151</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1513,10 +1510,10 @@
         <v>46165</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1527,30 +1524,38 @@
         <v>46249</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1558,89 +1563,89 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="B49" s="5">
+        <v>46133</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="D50" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="5">
-        <v>46133</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
@@ -1651,161 +1656,161 @@
         <v>87</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>88</v>
+      <c r="B54" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>89</v>
+      <c r="B55" s="5">
+        <v>46136</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>130</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B56" s="5">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>131</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B57" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>132</v>
+        <v>46151</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B58" s="5">
-        <v>46137</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>133</v>
+        <v>46188</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B59" s="5">
-        <v>46151</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>90</v>
+        <v>46191</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B60" s="5">
-        <v>46188</v>
-      </c>
-      <c r="C60" s="2" t="s">
+        <v>46193</v>
+      </c>
+      <c r="C60" s="9" t="s">
         <v>128</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61" s="5">
-        <v>46191</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>129</v>
+        <v>11</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="5">
-        <v>46193</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>130</v>
+        <v>11</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -1813,13 +1818,13 @@
         <v>11</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -1827,13 +1832,13 @@
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -1841,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -1855,13 +1860,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -1869,13 +1874,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -1883,13 +1888,13 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -1897,13 +1902,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -1911,13 +1916,13 @@
         <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -1925,112 +1930,112 @@
         <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="E77" s="7"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>50</v>
+      <c r="B79" s="5">
+        <v>46132</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E79" s="7"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -2038,87 +2043,60 @@
         <v>14</v>
       </c>
       <c r="B81" s="5">
-        <v>46132</v>
+        <v>46164</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>51</v>
+      <c r="B82" s="5">
+        <v>46218</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="B83" s="5">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="5">
-        <v>46218</v>
+      <c r="B84" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B85" s="5">
-        <v>46183</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E2 E34 E50 E79 D1:D1048576">
+  <autoFilter ref="A1:E84"/>
+  <conditionalFormatting sqref="E1:E2 E34 E48 E77 D1:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2130,7 +2108,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D84">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$83</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="140">
   <si>
     <t>Country</t>
   </si>
@@ -171,9 +171,6 @@
     <t>24-Apr-2026</t>
   </si>
   <si>
-    <t>02-Apr-2026</t>
-  </si>
-  <si>
     <t>18-Apr-2026</t>
   </si>
   <si>
@@ -339,9 +336,6 @@
     <t>HLX 100 Project - Rollout</t>
   </si>
   <si>
-    <t>Pre launch Campaign</t>
-  </si>
-  <si>
     <t>3S Inauguration – Lusaka</t>
   </si>
   <si>
@@ -430,9 +424,6 @@
   </si>
   <si>
     <t>Livingstone Riders Event</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zambia </t>
   </si>
   <si>
     <t>Service Camp</t>
@@ -892,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -913,10 +904,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -927,13 +918,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -944,10 +935,10 @@
         <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -958,10 +949,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -972,10 +963,10 @@
         <v>46122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -986,10 +977,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -1000,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1014,10 +1005,10 @@
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1028,10 +1019,10 @@
         <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1042,10 +1033,10 @@
         <v>46185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1056,10 +1047,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1070,10 +1061,10 @@
         <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1084,10 +1075,10 @@
         <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1098,10 +1089,10 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1112,10 +1103,10 @@
         <v>46158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1126,10 +1117,10 @@
         <v>46167</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1140,10 +1131,10 @@
         <v>46203</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1154,10 +1145,10 @@
         <v>46259</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1168,10 +1159,10 @@
         <v>31</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1182,10 +1173,10 @@
         <v>46079</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1196,10 +1187,10 @@
         <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1210,10 +1201,10 @@
         <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1224,10 +1215,10 @@
         <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1238,10 +1229,10 @@
         <v>46213</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1252,10 +1243,10 @@
         <v>38</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1266,10 +1257,10 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1280,10 +1271,10 @@
         <v>46188</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1294,10 +1285,10 @@
         <v>46179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1308,10 +1299,10 @@
         <v>46201</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1322,10 +1313,10 @@
         <v>46205</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1336,10 +1327,10 @@
         <v>46399</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1350,10 +1341,10 @@
         <v>46198</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -1364,10 +1355,10 @@
         <v>46073</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -1378,13 +1369,13 @@
         <v>28</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1395,10 +1386,10 @@
         <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1409,10 +1400,10 @@
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1423,10 +1414,10 @@
         <v>23</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -1437,10 +1428,10 @@
         <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -1451,10 +1442,10 @@
         <v>41</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -1465,13 +1456,13 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -1482,10 +1473,10 @@
         <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -1496,10 +1487,10 @@
         <v>46151</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -1510,10 +1501,10 @@
         <v>46165</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -1524,10 +1515,10 @@
         <v>46249</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -1538,10 +1529,10 @@
         <v>18</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -1552,10 +1543,10 @@
         <v>24</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -1566,10 +1557,10 @@
         <v>30</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -1580,13 +1571,13 @@
         <v>43</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1597,10 +1588,10 @@
         <v>46133</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1611,10 +1602,10 @@
         <v>32</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1625,10 +1616,10 @@
         <v>44</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1639,10 +1630,10 @@
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1653,10 +1644,10 @@
         <v>45</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -1667,10 +1658,10 @@
         <v>46136</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -1681,10 +1672,10 @@
         <v>46136</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1695,10 +1686,10 @@
         <v>46137</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1709,10 +1700,10 @@
         <v>46151</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -1723,10 +1714,10 @@
         <v>46188</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -1737,10 +1728,10 @@
         <v>46191</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -1751,10 +1742,10 @@
         <v>46193</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -1765,10 +1756,10 @@
         <v>46</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -1779,10 +1770,10 @@
         <v>39</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -1793,10 +1784,10 @@
         <v>32</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -1807,13 +1798,13 @@
         <v>44</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -1821,13 +1812,13 @@
         <v>33</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -1835,13 +1826,13 @@
         <v>47</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
@@ -1849,13 +1840,13 @@
         <v>47</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -1863,13 +1854,13 @@
         <v>28</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -1877,13 +1868,13 @@
         <v>36</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
@@ -1891,13 +1882,13 @@
         <v>37</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
@@ -1905,13 +1896,13 @@
         <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -1919,13 +1910,13 @@
         <v>48</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -1933,13 +1924,13 @@
         <v>21</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -1947,13 +1938,13 @@
         <v>21</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>13</v>
       </c>
@@ -1961,13 +1952,13 @@
         <v>37</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>13</v>
       </c>
@@ -1975,67 +1966,66 @@
         <v>18</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E77" s="7"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>20</v>
+      <c r="B78" s="5">
+        <v>46132</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B79" s="5">
-        <v>46132</v>
+      <c r="B79" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>50</v>
+      <c r="B80" s="5">
+        <v>46164</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -2043,13 +2033,13 @@
         <v>14</v>
       </c>
       <c r="B81" s="5">
-        <v>46164</v>
+        <v>46218</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -2057,46 +2047,32 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46218</v>
+        <v>46183</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B83" s="5">
-        <v>46183</v>
+        <v>14</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
-  <conditionalFormatting sqref="E1:E2 E34 E48 E77 D1:D1048576">
+  <autoFilter ref="A1:E83"/>
+  <conditionalFormatting sqref="E1:E2 E34 E48 D1:D1048576">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2108,7 +2084,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D84">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$88</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="147">
   <si>
     <t>Country</t>
   </si>
@@ -399,12 +399,6 @@
     <t>Bikers WareHouse Store Inauguration</t>
   </si>
   <si>
-    <t>I-Qube Launch</t>
-  </si>
-  <si>
-    <t>NTORQ150 &amp; RAIDER i-Go Launch</t>
-  </si>
-  <si>
     <t>Riding School Collaboration with King Donut</t>
   </si>
   <si>
@@ -420,9 +414,6 @@
     <t>Zambia Product line Launch</t>
   </si>
   <si>
-    <t>HLX DAY</t>
-  </si>
-  <si>
     <t>Livingstone Riders Event</t>
   </si>
   <si>
@@ -442,6 +433,36 @@
   </si>
   <si>
     <t>RR 310 Launch &amp; AOG Flag off</t>
+  </si>
+  <si>
+    <t>HLX DAY Kisangani</t>
+  </si>
+  <si>
+    <t>EKROLD - Duran Dealer opening &amp; Activation</t>
+  </si>
+  <si>
+    <t>George Dealer Activation Program</t>
+  </si>
+  <si>
+    <t>Breakfast ride with Apache owners and Women Riders</t>
+  </si>
+  <si>
+    <t>Tamatave Coco Opening</t>
+  </si>
+  <si>
+    <t>Fort Dhaupin Festival Mandrae Participation</t>
+  </si>
+  <si>
+    <t>11-15-May-2026</t>
+  </si>
+  <si>
+    <t>Executed Successfully</t>
+  </si>
+  <si>
+    <t>TVS Centurion Inauguration &amp; Test Ride</t>
+  </si>
+  <si>
+    <t>Boda Girls Launch</t>
   </si>
 </sst>
 </file>
@@ -883,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -1002,7 +1023,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>56</v>
@@ -1033,7 +1054,7 @@
         <v>46185</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>111</v>
@@ -1103,7 +1124,7 @@
         <v>46158</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>111</v>
@@ -1131,7 +1152,7 @@
         <v>46203</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>111</v>
@@ -1260,7 +1281,7 @@
         <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1268,10 +1289,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="5">
-        <v>46188</v>
+        <v>46163</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>111</v>
@@ -1282,10 +1303,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="5">
-        <v>46179</v>
+        <v>46188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>111</v>
@@ -1296,10 +1317,10 @@
         <v>5</v>
       </c>
       <c r="B29" s="5">
-        <v>46201</v>
+        <v>46193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>111</v>
@@ -1310,10 +1331,10 @@
         <v>5</v>
       </c>
       <c r="B30" s="5">
-        <v>46205</v>
+        <v>46201</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>111</v>
@@ -1324,10 +1345,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="5">
-        <v>46399</v>
+        <v>46205</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>111</v>
@@ -1338,10 +1359,10 @@
         <v>5</v>
       </c>
       <c r="B32" s="5">
-        <v>46198</v>
+        <v>46399</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>111</v>
@@ -1349,33 +1370,30 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" s="5">
-        <v>46073</v>
+        <v>46198</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>28</v>
+      <c r="B34" s="5">
+        <v>46073</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -1383,13 +1401,16 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -1397,13 +1418,13 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -1411,10 +1432,10 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>111</v>
@@ -1422,58 +1443,55 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46163</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46192</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="B41" s="5">
+        <v>46198</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>111</v>
@@ -1483,53 +1501,56 @@
       <c r="A42" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="5">
-        <v>46151</v>
+      <c r="B42" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="5">
-        <v>46165</v>
+      <c r="B43" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="5">
-        <v>46249</v>
+      <c r="B44" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>111</v>
@@ -1537,13 +1558,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46151</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -1551,13 +1572,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>30</v>
+        <v>7</v>
+      </c>
+      <c r="B47" s="5">
+        <v>46165</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -1565,257 +1586,260 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46249</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
+      <c r="D52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B53" s="5">
         <v>46133</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>127</v>
+      <c r="B54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="5">
-        <v>46136</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>128</v>
+      <c r="B55" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="5">
-        <v>46137</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>129</v>
+      <c r="B56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="5">
-        <v>46151</v>
+      <c r="B57" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B58" s="5">
-        <v>46188</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>124</v>
+        <v>46136</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B59" s="5">
-        <v>46191</v>
+        <v>46136</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B60" s="5">
-        <v>46193</v>
+        <v>46137</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
+      </c>
+      <c r="B61" s="5">
+        <v>46151</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>39</v>
+        <v>10</v>
+      </c>
+      <c r="B62" s="5">
+        <v>46164</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="B63" s="5">
+        <v>46188</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="B64" s="5">
+        <v>46180</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>138</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="B65" s="5">
+        <v>46193</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -1823,13 +1847,13 @@
         <v>11</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -1837,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -1851,10 +1875,10 @@
         <v>11</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>110</v>
@@ -1865,10 +1889,10 @@
         <v>11</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>110</v>
@@ -1879,10 +1903,10 @@
         <v>11</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>110</v>
@@ -1893,13 +1917,13 @@
         <v>11</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -1907,10 +1931,10 @@
         <v>11</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>111</v>
@@ -1921,52 +1945,52 @@
         <v>11</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>111</v>
@@ -1974,41 +1998,41 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="5">
-        <v>46132</v>
+        <v>11</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>111</v>
@@ -2016,13 +2040,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="5">
-        <v>46164</v>
+        <v>13</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>111</v>
@@ -2030,13 +2054,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="5">
-        <v>46218</v>
+        <v>13</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>111</v>
@@ -2046,33 +2070,103 @@
       <c r="A82" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B82" s="5">
-        <v>46183</v>
+      <c r="B82" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="5">
+        <v>46132</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="5">
+        <v>46164</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E83"/>
-  <conditionalFormatting sqref="E1:E2 E34 E48 D1:D1048576">
+  <autoFilter ref="A1:E88"/>
+  <conditionalFormatting sqref="E1:E2 E35 D1:D1048576 E52:E53">
     <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2084,7 +2178,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D83">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D88">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="146">
   <si>
     <t>Country</t>
   </si>
@@ -451,9 +451,6 @@
   </si>
   <si>
     <t>Fort Dhaupin Festival Mandrae Participation</t>
-  </si>
-  <si>
-    <t>11-15-May-2026</t>
   </si>
   <si>
     <t>Executed Successfully</t>
@@ -1022,8 +1019,8 @@
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>143</v>
+      <c r="B8" s="5">
+        <v>46153</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>56</v>
@@ -1292,7 +1289,7 @@
         <v>46163</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>111</v>
@@ -1671,7 +1668,7 @@
         <v>109</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -1794,7 +1791,7 @@
         <v>46164</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>111</v>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="155">
   <si>
     <t>Country</t>
   </si>
@@ -484,13 +484,16 @@
   </si>
   <si>
     <t>Apache 180, NTORQ Launch</t>
+  </si>
+  <si>
+    <t>The initiative was unveiled in Ahero, Kisumu County, amid growing concern over maternal deaths, weak rural healthcare access and insecurity facing female passengers in Kenya’s boda boda sector. In the first phase, TVS through Car &amp; General donated 32 TVS HLX 125 motorcycles to Boda Girls Kenya to help enforce last mile transport to healthcare facilities</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +515,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -549,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -565,32 +580,17 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF16AA06"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill>
@@ -1556,9 +1556,11 @@
       <c r="D25" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E25" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1571,7 +1573,9 @@
       <c r="D26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="3"/>
+      <c r="E26" s="10" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
@@ -1586,7 +1590,7 @@
       <c r="D27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
@@ -2680,134 +2684,134 @@
   </sheetData>
   <autoFilter ref="A1:E98"/>
   <conditionalFormatting sqref="E1:E2 E60 D92:D93 E33:E36 E52:E56 D1:D73 D80 D97 D82:D90 D99:D1048576">
-    <cfRule type="cellIs" dxfId="41" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="46" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="47" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="48" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D91">
-    <cfRule type="cellIs" dxfId="38" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="38" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="39" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78">
-    <cfRule type="cellIs" dxfId="35" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="35" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="36" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D76">
-    <cfRule type="cellIs" dxfId="32" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="33" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D77">
-    <cfRule type="cellIs" dxfId="29" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="29" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75">
-    <cfRule type="cellIs" dxfId="26" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="26" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="27" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D74">
-    <cfRule type="cellIs" dxfId="23" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="23" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="24" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79">
-    <cfRule type="cellIs" dxfId="20" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81">
-    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D94">
-    <cfRule type="cellIs" dxfId="14" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D96">
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Postponed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="167">
   <si>
     <t>Country</t>
   </si>
@@ -487,6 +487,42 @@
   </si>
   <si>
     <t>The initiative was unveiled in Ahero, Kisumu County, amid growing concern over maternal deaths, weak rural healthcare access and insecurity facing female passengers in Kenya’s boda boda sector. In the first phase, TVS through Car &amp; General donated 32 TVS HLX 125 motorcycles to Boda Girls Kenya to help enforce last mile transport to healthcare facilities</t>
+  </si>
+  <si>
+    <t>Category of Event</t>
+  </si>
+  <si>
+    <t>Service Activity</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>CSR</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Network Expansion</t>
+  </si>
+  <si>
+    <t>Experiential Event - Community Building</t>
+  </si>
+  <si>
+    <t>Product Launch</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>Brand Launch</t>
+  </si>
+  <si>
+    <t>Requires PR</t>
+  </si>
+  <si>
+    <t>Ronin Launch</t>
   </si>
 </sst>
 </file>
@@ -529,15 +565,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -560,11 +602,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -580,12 +636,17 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1169,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.1796875" customWidth="1"/>
@@ -1177,1513 +1238,2123 @@
     <col min="3" max="3" width="66.453125" customWidth="1"/>
     <col min="4" max="4" width="16.6328125" customWidth="1"/>
     <col min="5" max="5" width="124.54296875" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>46122</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
+      <c r="D7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>46153</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+      <c r="D8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>46185</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
+      <c r="D10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
+      <c r="D11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>46207</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
+      <c r="D15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>46202</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
+      <c r="D16" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>46259</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
+      <c r="D17" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="6">
         <v>46079</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3" t="s">
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
+      <c r="E21" s="4"/>
+      <c r="F21" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3" t="s">
+      <c r="E22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="7">
         <v>46213</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3" t="s">
+      <c r="D23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3" t="s">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3" t="s">
+      <c r="F25" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="7">
         <v>46163</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>101</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3" t="s">
+      <c r="F26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="7">
         <v>46188</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="7">
         <v>46193</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="7">
         <v>46201</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3" t="s">
+      <c r="D29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="7">
         <v>46214</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="7">
         <v>46399</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3" t="s">
+      <c r="D31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="7">
         <v>46198</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3" t="s">
+      <c r="D32" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="7">
         <v>46073</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3" t="s">
+      <c r="F33" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="5" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="3" t="s">
+      <c r="F34" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3" t="s">
+      <c r="F35" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="3" t="s">
+      <c r="F36" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="7">
         <v>46195</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3" t="s">
+      <c r="D37" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="7">
         <v>46228</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="7">
         <v>46197</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="3" t="s">
+      <c r="D39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="7">
         <v>46215</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="3" t="s">
+      <c r="D40" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="3" t="s">
+      <c r="E41" s="4"/>
+      <c r="F41" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3" t="s">
+      <c r="E42" s="4"/>
+      <c r="F42" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="3" t="s">
+      <c r="F43" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3" t="s">
+      <c r="D44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="7">
         <v>46151</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="3" t="s">
+      <c r="D45" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="7">
         <v>46185</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="3" t="s">
+      <c r="D46" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="7">
         <v>46249</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
+      <c r="D47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="14">
+        <v>46280</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="7">
         <v>46342</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C49" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3" t="s">
+      <c r="D49" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="3" t="s">
+      <c r="D50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="3" t="s">
+      <c r="D51" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3" t="s">
+      <c r="D52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D53" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E53" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="3" t="s">
+      <c r="F53" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B54" s="7">
         <v>46133</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D54" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E54" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3" t="s">
+      <c r="F54" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E55" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="3" t="s">
+      <c r="F55" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E56" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="3" t="s">
+      <c r="F56" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E57" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3" t="s">
+      <c r="F57" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B58" s="7">
         <v>46200</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3" t="s">
+      <c r="D58" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B59" s="7">
         <v>46136</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E59" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3" t="s">
+      <c r="F59" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B60" s="7">
         <v>46137</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C60" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="3" t="s">
+      <c r="D60" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B60" s="6">
+      <c r="B61" s="7">
         <v>46151</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E61" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3" t="s">
+      <c r="F61" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B61" s="6">
+      <c r="B62" s="7">
         <v>46249</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="3" t="s">
+      <c r="D62" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B62" s="6">
+      <c r="B63" s="7">
         <v>46210</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C63" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3" t="s">
+      <c r="D63" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B63" s="6">
+      <c r="B64" s="7">
         <v>46203</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C64" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="3" t="s">
+      <c r="D64" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D65" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="3" t="s">
+      <c r="E65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B66" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D66" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3" t="s">
+      <c r="E66" s="4"/>
+      <c r="F66" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B67" s="7">
         <v>46200</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C67" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="3" t="s">
+      <c r="D67" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="3" t="s">
+      <c r="E68" s="4"/>
+      <c r="F68" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="6">
+      <c r="B69" s="7">
         <v>46221</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C69" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="3" t="s">
+      <c r="D69" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="6">
+      <c r="B70" s="7">
         <v>46191</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="3" t="s">
+      <c r="D70" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B71" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D71" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="3" t="s">
+      <c r="E71" s="4"/>
+      <c r="F71" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D72" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="3" t="s">
+      <c r="E72" s="4"/>
+      <c r="F72" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B72" s="6">
+      <c r="B73" s="7">
         <v>46150</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D73" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="3" t="s">
+      <c r="E73" s="4"/>
+      <c r="F73" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="6">
+      <c r="B74" s="7">
         <v>46208</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="3" t="s">
+      <c r="D74" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B74" s="6">
+      <c r="B75" s="7">
         <v>46171</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C75" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="3" t="s">
+      <c r="D75" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="6">
+      <c r="B76" s="7">
         <v>46208</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C76" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="3" t="s">
+      <c r="D76" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B76" s="6">
+      <c r="B77" s="7">
         <v>46221</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="3" t="s">
+      <c r="D77" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B77" s="6">
+      <c r="B78" s="7">
         <v>46254</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C78" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="3" t="s">
+      <c r="D78" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="6">
+      <c r="B79" s="7">
         <v>46172</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C79" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="3" t="s">
+      <c r="D79" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="6">
+      <c r="B80" s="7">
         <v>46254</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="3" t="s">
+      <c r="D80" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B81" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C81" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D81" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="3" t="s">
+      <c r="E81" s="4"/>
+      <c r="F81" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B81" s="6">
+      <c r="B82" s="7">
         <v>46239</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="3" t="s">
+      <c r="D82" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B82" s="6">
+      <c r="B83" s="7">
         <v>46188</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="3" t="s">
+      <c r="D83" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B83" s="6">
+      <c r="B84" s="7">
         <v>46280</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="3" t="s">
+      <c r="D84" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B85" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C85" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D85" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="3" t="s">
+      <c r="E85" s="4"/>
+      <c r="F85" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B85" s="6">
+      <c r="B86" s="7">
         <v>46132</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D86" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="3" t="s">
+      <c r="E86" s="4"/>
+      <c r="F86" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B87" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C87" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="3" t="s">
+      <c r="D87" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B87" s="6">
+      <c r="B88" s="7">
         <v>46164</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C88" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="3" t="s">
+      <c r="D88" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B88" s="6">
+      <c r="B89" s="7">
         <v>46218</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C89" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="3" t="s">
+      <c r="D89" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B89" s="6">
+      <c r="B90" s="7">
         <v>46183</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C90" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="3" t="s">
+      <c r="D90" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B91" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C91" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B91" s="6">
-        <v>46254</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D91" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B92" s="6">
+      <c r="B92" s="7">
+        <v>46254</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B93" s="7">
         <v>46280</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C93" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="4" t="s">
+      <c r="D93" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="6">
+      <c r="B94" s="7">
         <v>46256</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C94" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="3" t="s">
+      <c r="D94" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B94" s="6">
+      <c r="B95" s="7">
         <v>46188</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C95" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="3" t="s">
+      <c r="D95" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="6">
+      <c r="B96" s="7">
         <v>46208</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C96" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B96" s="6">
-        <v>46198</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B97" s="6">
+      <c r="B97" s="7">
+        <v>46198</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="7">
         <v>46228</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C98" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="4" t="s">
+      <c r="D98" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B98" s="6">
+      <c r="B99" s="7">
         <v>46249</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C99" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E98" s="3"/>
+      <c r="D99" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>159</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E98"/>
-  <conditionalFormatting sqref="E1:E2 E60 D92:D93 E33:E36 E52:E56 D1:D73 D80 D97 D82:D90 D99:D1048576">
+  <autoFilter ref="A1:E99"/>
+  <conditionalFormatting sqref="E1:E2 E61 D93:D94 E33:E36 E53:E57 D1:D47 D81 D98 D83:D91 D100:D1048576 D49:D74">
     <cfRule type="cellIs" dxfId="38" priority="46" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2694,7 +3365,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D91">
+  <conditionalFormatting sqref="D92">
     <cfRule type="cellIs" dxfId="35" priority="37" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2705,7 +3376,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D78">
+  <conditionalFormatting sqref="D79">
     <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2716,7 +3387,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D76">
+  <conditionalFormatting sqref="D77">
     <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2727,7 +3398,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D77">
+  <conditionalFormatting sqref="D78">
     <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2738,7 +3409,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D75">
+  <conditionalFormatting sqref="D76">
     <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2749,7 +3420,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D74">
+  <conditionalFormatting sqref="D75">
     <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2760,7 +3431,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D79">
+  <conditionalFormatting sqref="D80">
     <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2771,7 +3442,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D81">
+  <conditionalFormatting sqref="D82">
     <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2782,7 +3453,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D94">
+  <conditionalFormatting sqref="D95">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2793,7 +3464,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D95">
+  <conditionalFormatting sqref="D96">
     <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2804,7 +3475,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D96">
+  <conditionalFormatting sqref="D97">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2815,7 +3486,7 @@
       <formula>"Executed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D98">
+  <conditionalFormatting sqref="D99">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Yet to Happen"</formula>
     </cfRule>
@@ -2827,7 +3498,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D47 D94:D96 D49:D91">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D50:D92 D95:D97 D2:D47">
       <formula1>"Executed, Postponed, Yet to Happen"</formula1>
     </dataValidation>
   </dataValidations>

--- a/NSE1 Important Dates.xlsx
+++ b/NSE1 Important Dates.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="168">
   <si>
     <t>Country</t>
   </si>
@@ -523,6 +523,9 @@
   </si>
   <si>
     <t>Ronin Launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembly line Expansion </t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1241,7 @@
     <col min="3" max="3" width="66.453125" customWidth="1"/>
     <col min="4" max="4" width="16.6328125" customWidth="1"/>
     <col min="5" max="5" width="124.54296875" customWidth="1"/>
-    <col min="6" max="6" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1280,10 +1283,10 @@
       <c r="E2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1301,11 +1304,11 @@
         <v>101</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>159</v>
+      <c r="F3" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1322,11 +1325,11 @@
         <v>102</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>159</v>
+      <c r="F4" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1343,10 +1346,10 @@
         <v>101</v>
       </c>
       <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1364,10 +1367,10 @@
         <v>103</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1385,11 +1388,11 @@
         <v>103</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>159</v>
+      <c r="F7" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1406,10 +1409,10 @@
         <v>103</v>
       </c>
       <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1427,10 +1430,10 @@
         <v>103</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1448,10 +1451,10 @@
         <v>103</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1469,10 +1472,10 @@
         <v>103</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1490,10 +1493,10 @@
         <v>103</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1511,11 +1514,11 @@
         <v>103</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>157</v>
+      <c r="F13" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1532,10 +1535,10 @@
         <v>101</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1553,10 +1556,10 @@
         <v>103</v>
       </c>
       <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1574,10 +1577,10 @@
         <v>103</v>
       </c>
       <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1595,10 +1598,10 @@
         <v>103</v>
       </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1616,11 +1619,11 @@
         <v>101</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>159</v>
+      <c r="F18" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1637,10 +1640,10 @@
         <v>102</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1658,10 +1661,10 @@
         <v>101</v>
       </c>
       <c r="E20" s="4"/>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1679,10 +1682,10 @@
         <v>101</v>
       </c>
       <c r="E21" s="4"/>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1700,11 +1703,11 @@
         <v>101</v>
       </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>159</v>
+      <c r="F22" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1721,10 +1724,10 @@
         <v>103</v>
       </c>
       <c r="E23" s="4"/>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1742,10 +1745,10 @@
         <v>101</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1765,11 +1768,11 @@
       <c r="E25" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>159</v>
+      <c r="F25" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1788,10 +1791,10 @@
       <c r="E26" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1809,10 +1812,10 @@
         <v>103</v>
       </c>
       <c r="E27" s="11"/>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1830,10 +1833,10 @@
         <v>103</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1851,10 +1854,10 @@
         <v>103</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1872,10 +1875,10 @@
         <v>103</v>
       </c>
       <c r="E30" s="4"/>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1893,11 +1896,11 @@
         <v>103</v>
       </c>
       <c r="E31" s="4"/>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>157</v>
+      <c r="G31" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1914,10 +1917,10 @@
         <v>103</v>
       </c>
       <c r="E32" s="4"/>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -1937,10 +1940,10 @@
       <c r="E33" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1960,10 +1963,10 @@
       <c r="E34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1983,11 +1986,11 @@
       <c r="E35" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>159</v>
+      <c r="F35" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2006,10 +2009,10 @@
       <c r="E36" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2027,10 +2030,10 @@
         <v>103</v>
       </c>
       <c r="E37" s="4"/>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2048,10 +2051,10 @@
         <v>103</v>
       </c>
       <c r="E38" s="4"/>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2069,10 +2072,10 @@
         <v>103</v>
       </c>
       <c r="E39" s="4"/>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2090,11 +2093,11 @@
         <v>103</v>
       </c>
       <c r="E40" s="4"/>
-      <c r="F40" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>159</v>
+      <c r="F40" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2111,10 +2114,10 @@
         <v>101</v>
       </c>
       <c r="E41" s="4"/>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2132,10 +2135,10 @@
         <v>101</v>
       </c>
       <c r="E42" s="4"/>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2155,10 +2158,10 @@
       <c r="E43" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2176,10 +2179,10 @@
         <v>103</v>
       </c>
       <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2197,10 +2200,10 @@
         <v>103</v>
       </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2218,10 +2221,10 @@
         <v>103</v>
       </c>
       <c r="E46" s="4"/>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2239,11 +2242,11 @@
         <v>103</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>157</v>
+      <c r="G47" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2281,10 +2284,10 @@
         <v>103</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2302,10 +2305,10 @@
         <v>103</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2323,10 +2326,10 @@
         <v>103</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2344,11 +2347,11 @@
         <v>103</v>
       </c>
       <c r="E52" s="4"/>
-      <c r="F52" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>157</v>
+      <c r="F52" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2367,10 +2370,10 @@
       <c r="E53" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2390,10 +2393,10 @@
       <c r="E54" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2413,10 +2416,10 @@
       <c r="E55" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2436,10 +2439,10 @@
       <c r="E56" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2459,10 +2462,10 @@
       <c r="E57" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2480,10 +2483,10 @@
         <v>103</v>
       </c>
       <c r="E58" s="4"/>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2503,10 +2506,10 @@
       <c r="E59" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2524,10 +2527,10 @@
         <v>103</v>
       </c>
       <c r="E60" s="4"/>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2547,11 +2550,11 @@
       <c r="E61" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>159</v>
+      <c r="F61" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2568,10 +2571,10 @@
         <v>103</v>
       </c>
       <c r="E62" s="4"/>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2589,10 +2592,10 @@
         <v>103</v>
       </c>
       <c r="E63" s="4"/>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2610,10 +2613,10 @@
         <v>103</v>
       </c>
       <c r="E64" s="4"/>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2631,11 +2634,11 @@
         <v>101</v>
       </c>
       <c r="E65" s="4"/>
-      <c r="F65" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>159</v>
+      <c r="F65" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G65" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2652,10 +2655,10 @@
         <v>101</v>
       </c>
       <c r="E66" s="4"/>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2673,10 +2676,10 @@
         <v>103</v>
       </c>
       <c r="E67" s="4"/>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2694,10 +2697,10 @@
         <v>102</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2715,10 +2718,10 @@
         <v>103</v>
       </c>
       <c r="E69" s="4"/>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2736,11 +2739,11 @@
         <v>103</v>
       </c>
       <c r="E70" s="4"/>
-      <c r="F70" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>159</v>
+      <c r="F70" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2757,10 +2760,10 @@
         <v>101</v>
       </c>
       <c r="E71" s="4"/>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2778,10 +2781,10 @@
         <v>101</v>
       </c>
       <c r="E72" s="4"/>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G72" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2799,11 +2802,11 @@
         <v>101</v>
       </c>
       <c r="E73" s="4"/>
-      <c r="F73" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>159</v>
+      <c r="F73" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2820,11 +2823,11 @@
         <v>103</v>
       </c>
       <c r="E74" s="4"/>
-      <c r="F74" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>159</v>
+      <c r="F74" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2841,10 +2844,10 @@
         <v>103</v>
       </c>
       <c r="E75" s="4"/>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2862,11 +2865,11 @@
         <v>103</v>
       </c>
       <c r="E76" s="4"/>
-      <c r="F76" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>159</v>
+      <c r="F76" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G76" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -2883,10 +2886,10 @@
         <v>103</v>
       </c>
       <c r="E77" s="4"/>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2904,10 +2907,10 @@
         <v>103</v>
       </c>
       <c r="E78" s="4"/>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2925,10 +2928,10 @@
         <v>103</v>
       </c>
       <c r="E79" s="4"/>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2946,10 +2949,10 @@
         <v>103</v>
       </c>
       <c r="E80" s="4"/>
-      <c r="F80" s="4" t="s">
+      <c r="F80" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2967,10 +2970,10 @@
         <v>101</v>
       </c>
       <c r="E81" s="4"/>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2988,10 +2991,10 @@
         <v>103</v>
       </c>
       <c r="E82" s="4"/>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3009,11 +3012,11 @@
         <v>103</v>
       </c>
       <c r="E83" s="4"/>
-      <c r="F83" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>159</v>
+      <c r="F83" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3030,10 +3033,10 @@
         <v>103</v>
       </c>
       <c r="E84" s="4"/>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3051,10 +3054,10 @@
         <v>101</v>
       </c>
       <c r="E85" s="4"/>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3072,10 +3075,10 @@
         <v>101</v>
       </c>
       <c r="E86" s="4"/>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3093,10 +3096,10 @@
         <v>103</v>
       </c>
       <c r="E87" s="4"/>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3114,10 +3117,10 @@
         <v>103</v>
       </c>
       <c r="E88" s="4"/>
-      <c r="F88" s="4" t="s">
+      <c r="F88" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3135,10 +3138,10 @@
         <v>103</v>
       </c>
       <c r="E89" s="4"/>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3156,10 +3159,10 @@
         <v>103</v>
       </c>
       <c r="E90" s="4"/>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3177,10 +3180,10 @@
         <v>103</v>
       </c>
       <c r="E91" s="4"/>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3198,10 +3201,10 @@
         <v>103</v>
       </c>
       <c r="E92" s="4"/>
-      <c r="F92" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G92" s="4" t="s">
+      <c r="F92" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G92" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3219,10 +3222,10 @@
         <v>103</v>
       </c>
       <c r="E93" s="4"/>
-      <c r="F93" s="4" t="s">
+      <c r="F93" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3240,10 +3243,10 @@
         <v>103</v>
       </c>
       <c r="E94" s="4"/>
-      <c r="F94" s="4" t="s">
+      <c r="F94" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="12" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3261,10 +3264,10 @@
         <v>103</v>
       </c>
       <c r="E95" s="4"/>
-      <c r="F95" s="4" t="s">
+      <c r="F95" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3282,10 +3285,10 @@
         <v>103</v>
       </c>
       <c r="E96" s="4"/>
-      <c r="F96" s="4" t="s">
+      <c r="F96" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3303,10 +3306,10 @@
         <v>103</v>
       </c>
       <c r="E97" s="4"/>
-      <c r="F97" s="4" t="s">
+      <c r="F97" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3324,10 +3327,10 @@
         <v>103</v>
       </c>
       <c r="E98" s="4"/>
-      <c r="F98" s="4" t="s">
+      <c r="F98" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" s="12" t="s">
         <v>157</v>
       </c>
     </row>
@@ -3345,10 +3348,10 @@
         <v>103</v>
       </c>
       <c r="E99" s="4"/>
-      <c r="F99" s="4" t="s">
+      <c r="F99" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" s="12" t="s">
         <v>159</v>
       </c>
     </row>
